--- a/static/Military service_template.xlsx
+++ b/static/Military service_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\MPR-vg-ifm\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chung.vo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8ADB0E-AA54-4FE0-A254-42CA85B27FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F134C2E-419B-4A9D-B763-25CA06303745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="3" r:id="rId1"/>
@@ -27,42 +27,36 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>EMPNO</t>
-  </si>
-  <si>
-    <t>NAME_S</t>
-  </si>
-  <si>
-    <t>DEPT_NO</t>
-  </si>
-  <si>
-    <t>DEPT NAME</t>
-  </si>
-  <si>
-    <t>POSITION</t>
-  </si>
-  <si>
-    <t>MILITARY SERVICE START DATE</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">DANH SÁCH NHÂN VIÊN THỰC HIỆN NGHĨA VỤ QUÂN SỰ
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>履行兵役員工名單</t>
-    </r>
+    <t>STT
+NO.</t>
+  </si>
+  <si>
+    <t>Số thẻ CNV
+EMPNO</t>
+  </si>
+  <si>
+    <t>Họ tên
+NAME_S</t>
+  </si>
+  <si>
+    <t>Mã Bộ phận
+DEPT_NO</t>
+  </si>
+  <si>
+    <t>Tên Bộ phận
+DEPT NAME</t>
+  </si>
+  <si>
+    <t>Vị trí
+POSITION</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu thực hiện nghĩa vụ quân sự
+MILITARY SERVICE START DATE</t>
+  </si>
+  <si>
+    <t>DANH SÁCH CÔNG NHÂN VIÊN THỰC HIỆN NGHĨA VỤ QUÂN SỰ
+LIST OF EMPLOYEES PERFORMING MILITARY SERVICE</t>
   </si>
 </sst>
 </file>
@@ -72,26 +66,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -109,6 +87,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,22 +137,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -180,7 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -451,11 +436,11 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="39.140625" style="7" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="9" customWidth="1"/>
     <col min="5" max="6" width="40.85546875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.42578125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
